--- a/grupos/1DM - Estadisticos 20211.xlsx
+++ b/grupos/1DM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="181">
   <si>
     <t>Materia</t>
   </si>
@@ -218,18 +218,18 @@
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
+    <t>Morales Vallejo Jorge Luis</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>Morales Vallejo Jorge Luis</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -245,19 +245,106 @@
     <t>ALDUCIN</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HIDALGO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ONOFRE</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>TERCERO</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ARCADIO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>NAVA</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>MELANI PAOLA</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>ANA LILIANA</t>
+  </si>
+  <si>
+    <t>RICARDO ABEL</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>MARIANA PAOLA</t>
+  </si>
+  <si>
+    <t>ANGELICA NAOMI</t>
+  </si>
+  <si>
+    <t>CARLOS ROBERTO</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
     <t>ARGÜELLO</t>
   </si>
   <si>
+    <t>CRESCENCIO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HIDALGO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
   </si>
   <si>
     <t>MADRAZO</t>
@@ -266,25 +353,31 @@
     <t>MORALES</t>
   </si>
   <si>
-    <t>ONOFRE</t>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>PATIÑO</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>TERCERO</t>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
   </si>
   <si>
     <t>TELLEZ</t>
@@ -293,28 +386,46 @@
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>VALLEJO</t>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VENEGAS</t>
   </si>
   <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
     <t>NARANJO</t>
   </si>
   <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>PETRILLI</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
   </si>
   <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>ARCADIO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
   </si>
   <si>
     <t>0</t>
@@ -323,49 +434,73 @@
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
+    <t>BENITO</t>
   </si>
   <si>
     <t>APONTE</t>
   </si>
   <si>
-    <t>NAVA</t>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
   </si>
   <si>
     <t>ZEPEDA</t>
   </si>
   <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
+    <t>ARAUZ</t>
   </si>
   <si>
     <t>ARELLANO</t>
   </si>
   <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>AMECA</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>MELANI PAOLA</t>
+    <t>YARELI</t>
   </si>
   <si>
     <t>ATZIN HEFZIBA</t>
   </si>
   <si>
+    <t>NADIA</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>SUGHEYDI JAZMIN</t>
+  </si>
+  <si>
     <t>LIZBETH</t>
   </si>
   <si>
-    <t>ABIGAIL</t>
+    <t>EMILIANO</t>
+  </si>
+  <si>
+    <t>LESLY JAREDT</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
   </si>
   <si>
     <t>ANGEL SAMUEL</t>
   </si>
   <si>
-    <t>ANA LILIANA</t>
-  </si>
-  <si>
-    <t>RICARDO ABEL</t>
+    <t>VENUS</t>
+  </si>
+  <si>
+    <t>BIBIAN YANEL</t>
   </si>
   <si>
     <t>ANGELO RENE</t>
@@ -374,25 +509,40 @@
     <t>DULCE MARIA</t>
   </si>
   <si>
-    <t>LUIS ARMANDO</t>
+    <t>DULCE NAOMI</t>
+  </si>
+  <si>
+    <t>ALYN</t>
   </si>
   <si>
     <t>NATALIA</t>
   </si>
   <si>
-    <t>MARIANA PAOLA</t>
-  </si>
-  <si>
-    <t>ANGELICA NAOMI</t>
+    <t>MILDRED MARIANA</t>
+  </si>
+  <si>
+    <t>DUILIO</t>
+  </si>
+  <si>
+    <t>VIRIDIANA</t>
+  </si>
+  <si>
+    <t>JAQUELINE</t>
+  </si>
+  <si>
+    <t>JOSE ANGEL</t>
   </si>
   <si>
     <t>BRYAN ABRAHAM</t>
   </si>
   <si>
-    <t>CARLOS ROBERTO</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
+    <t>ARANTXA</t>
+  </si>
+  <si>
+    <t>ISAI</t>
+  </si>
+  <si>
+    <t>BETHSABE</t>
   </si>
   <si>
     <t>VIANEY</t>
@@ -401,166 +551,16 @@
     <t>RICARDO</t>
   </si>
   <si>
-    <t>FERNANDO</t>
+    <t>MAGDA SARAY</t>
+  </si>
+  <si>
+    <t>KARLA GRISELL</t>
+  </si>
+  <si>
+    <t>EZEQUIEL</t>
   </si>
   <si>
     <t>NANCY PAOLA</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>CRESCENCIO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>PATIÑO</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>PETRILLI</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>BENITO</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>ARAUZ</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>AMECA</t>
-  </si>
-  <si>
-    <t>YARELI</t>
-  </si>
-  <si>
-    <t>NADIA</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>SUGHEYDI JAZMIN</t>
-  </si>
-  <si>
-    <t>EMILIANO</t>
-  </si>
-  <si>
-    <t>LESLY JAREDT</t>
-  </si>
-  <si>
-    <t>MARIA TERESA</t>
-  </si>
-  <si>
-    <t>VENUS</t>
-  </si>
-  <si>
-    <t>BIBIAN YANEL</t>
-  </si>
-  <si>
-    <t>DULCE NAOMI</t>
-  </si>
-  <si>
-    <t>ALYN</t>
-  </si>
-  <si>
-    <t>MILDRED MARIANA</t>
-  </si>
-  <si>
-    <t>DUILIO</t>
-  </si>
-  <si>
-    <t>VIRIDIANA</t>
-  </si>
-  <si>
-    <t>JAQUELINE</t>
-  </si>
-  <si>
-    <t>JOSE ANGEL</t>
-  </si>
-  <si>
-    <t>ARANTXA</t>
-  </si>
-  <si>
-    <t>ISAI</t>
-  </si>
-  <si>
-    <t>BETHSABE</t>
-  </si>
-  <si>
-    <t>MAGDA SARAY</t>
-  </si>
-  <si>
-    <t>KARLA GRISELL</t>
-  </si>
-  <si>
-    <t>EZEQUIEL</t>
   </si>
 </sst>
 </file>
@@ -1067,19 +1067,19 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1103,10 +1103,10 @@
         <v>9</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -1126,34 +1126,34 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>-1</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1180,19 +1180,19 @@
         <v>5</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
         <v>-1</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1206,7 +1206,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -1221,19 +1221,19 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1260,13 +1260,13 @@
         <v>7</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
         <v>6</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>6</v>
@@ -1298,19 +1298,19 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1337,13 +1337,13 @@
         <v>10</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>10</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1375,19 +1375,19 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1411,19 +1411,19 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>10</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1452,19 +1452,19 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1488,13 +1488,13 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>7</v>
@@ -1529,19 +1529,19 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1571,10 +1571,10 @@
         <v>8</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -1591,7 +1591,7 @@
         <v>9</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E11">
         <v>7</v>
@@ -1606,10 +1606,10 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1618,7 +1618,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1642,10 +1642,10 @@
         <v>8</v>
       </c>
       <c r="U11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -1683,19 +1683,19 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1719,10 +1719,10 @@
         <v>9</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -1760,19 +1760,19 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1799,10 +1799,10 @@
         <v>9</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>6</v>
@@ -1837,19 +1837,19 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1873,7 +1873,7 @@
         <v>8</v>
       </c>
       <c r="U14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>9</v>
@@ -1899,16 +1899,16 @@
         <v>-1</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E15">
         <v>-1</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H15">
         <v>-1</v>
@@ -1917,13 +1917,13 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1953,16 +1953,16 @@
         <v>-1</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W15">
         <v>-1</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1976,7 +1976,7 @@
         <v>6</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -1991,19 +1991,19 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2027,16 +2027,16 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>6</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -2053,13 +2053,13 @@
         <v>8</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G17">
         <v>7</v>
@@ -2068,16 +2068,16 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2107,13 +2107,13 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -2145,13 +2145,13 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -2181,10 +2181,10 @@
         <v>8</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -2204,19 +2204,19 @@
         <v>7</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H19">
         <v>-1</v>
@@ -2225,16 +2225,16 @@
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2258,19 +2258,19 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2284,16 +2284,16 @@
         <v>-1</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E20">
         <v>-1</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -2302,7 +2302,7 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2338,16 +2338,16 @@
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>-1</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2376,19 +2376,19 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2415,13 +2415,13 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>6</v>
@@ -2435,10 +2435,10 @@
         <v>8</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>10</v>
@@ -2453,19 +2453,19 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2489,10 +2489,10 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>10</v>
@@ -2530,19 +2530,19 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2569,13 +2569,13 @@
         <v>9</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>9</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2592,13 +2592,13 @@
         <v>6</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E24">
         <v>-1</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G24">
         <v>-1</v>
@@ -2610,7 +2610,7 @@
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2646,13 +2646,13 @@
         <v>6</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W24">
         <v>-1</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>-1</v>
@@ -2684,19 +2684,19 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2723,7 +2723,7 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2755,25 +2755,25 @@
         <v>7</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H26">
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2800,16 +2800,16 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>10</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2838,19 +2838,19 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2877,7 +2877,7 @@
         <v>9</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -2886,7 +2886,7 @@
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2900,16 +2900,16 @@
         <v>-1</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H28">
         <v>-1</v>
@@ -2918,13 +2918,13 @@
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2954,16 +2954,16 @@
         <v>-1</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2977,16 +2977,16 @@
         <v>8</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E29">
         <v>-1</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H29">
         <v>-1</v>
@@ -2995,7 +2995,7 @@
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
         <v>-1</v>
@@ -3031,16 +3031,16 @@
         <v>8</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W29">
         <v>-1</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3069,19 +3069,19 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3108,13 +3108,13 @@
         <v>8</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>9</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>6</v>
@@ -3146,19 +3146,19 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3182,7 +3182,7 @@
         <v>9</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -3191,10 +3191,10 @@
         <v>10</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y31">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3223,19 +3223,19 @@
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3262,7 +3262,7 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>10</v>
@@ -3271,7 +3271,7 @@
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3300,19 +3300,19 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3336,16 +3336,16 @@
         <v>8</v>
       </c>
       <c r="U33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>9</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y33">
         <v>8</v>
@@ -3362,7 +3362,7 @@
         <v>6</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E34">
         <v>6</v>
@@ -3371,25 +3371,25 @@
         <v>7</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H34">
         <v>-1</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3413,19 +3413,19 @@
         <v>6</v>
       </c>
       <c r="U34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X34">
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3454,19 +3454,19 @@
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3493,13 +3493,13 @@
         <v>9</v>
       </c>
       <c r="V35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y35">
         <v>7</v>
@@ -3531,19 +3531,19 @@
         <v>-1</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3570,16 +3570,16 @@
         <v>10</v>
       </c>
       <c r="V36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>9</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3608,19 +3608,19 @@
         <v>-1</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3650,13 +3650,13 @@
         <v>9</v>
       </c>
       <c r="W37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>10</v>
       </c>
       <c r="Y37">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3673,7 +3673,7 @@
         <v>6</v>
       </c>
       <c r="E38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F38">
         <v>8</v>
@@ -3685,16 +3685,16 @@
         <v>-1</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M38">
         <v>-1</v>
@@ -3727,7 +3727,7 @@
         <v>6</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X38">
         <v>8</v>
@@ -3747,16 +3747,16 @@
         <v>-1</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E39">
         <v>6</v>
       </c>
       <c r="F39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H39">
         <v>-1</v>
@@ -3765,13 +3765,13 @@
         <v>-1</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K39">
         <v>-1</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M39">
         <v>-1</v>
@@ -3801,16 +3801,16 @@
         <v>-1</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W39">
         <v>6</v>
       </c>
       <c r="X39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3824,25 +3824,25 @@
         <v>6</v>
       </c>
       <c r="D40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E40">
         <v>-1</v>
       </c>
       <c r="F40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H40">
         <v>-1</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K40">
         <v>-1</v>
@@ -3878,16 +3878,16 @@
         <v>6</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W40">
         <v>-1</v>
       </c>
       <c r="X40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y40">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3901,31 +3901,31 @@
         <v>6</v>
       </c>
       <c r="D41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E41">
         <v>-1</v>
       </c>
       <c r="F41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H41">
         <v>-1</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K41">
         <v>-1</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M41">
         <v>-1</v>
@@ -3955,16 +3955,16 @@
         <v>6</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W41">
         <v>-1</v>
       </c>
       <c r="X41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y41">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3993,19 +3993,19 @@
         <v>-1</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -4029,16 +4029,16 @@
         <v>7</v>
       </c>
       <c r="U42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W42">
         <v>7</v>
       </c>
       <c r="X42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y42">
         <v>7</v>
@@ -4055,7 +4055,7 @@
         <v>7</v>
       </c>
       <c r="D43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E43">
         <v>6</v>
@@ -4064,25 +4064,25 @@
         <v>6</v>
       </c>
       <c r="G43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H43">
         <v>-1</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -4109,16 +4109,16 @@
         <v>7</v>
       </c>
       <c r="V43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W43">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X43">
         <v>6</v>
       </c>
       <c r="Y43">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -4147,19 +4147,19 @@
         <v>-1</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K44">
         <v>-1</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N44">
         <v>-1</v>
@@ -4218,25 +4218,25 @@
         <v>7</v>
       </c>
       <c r="G45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H45">
         <v>-1</v>
       </c>
       <c r="I45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N45">
         <v>-1</v>
@@ -4263,16 +4263,16 @@
         <v>7</v>
       </c>
       <c r="V45">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W45">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X45">
         <v>7</v>
       </c>
       <c r="Y45">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:25">
@@ -4301,16 +4301,16 @@
         <v>-1</v>
       </c>
       <c r="I46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M46">
         <v>-1</v>
@@ -4337,13 +4337,13 @@
         <v>8</v>
       </c>
       <c r="U46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W46">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X46">
         <v>7</v>
@@ -4414,25 +4414,25 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E2">
+        <v>12</v>
+      </c>
+      <c r="F2">
+        <v>72.09</v>
+      </c>
+      <c r="G2">
+        <v>27.91</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>60.47</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>7.4</v>
-      </c>
-      <c r="I2">
-        <v>17</v>
-      </c>
-      <c r="J2">
-        <v>39.53</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4446,30 +4446,30 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>67.44</v>
+        <v>72.09</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>25.58</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="I3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>32.56</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -4478,30 +4478,30 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>74.42</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>16.28</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>25.58</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
@@ -4510,30 +4510,30 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>74.42</v>
+        <v>83.72</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>25.58</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
@@ -4542,30 +4542,30 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>79.06999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="G6">
-        <v>16.28</v>
+        <v>2.33</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>4.65</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>69</v>
@@ -4574,25 +4574,25 @@
         <v>43</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>90.7</v>
+      </c>
+      <c r="G7">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H7">
+        <v>7.3</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>83.72</v>
-      </c>
-      <c r="G7">
+      <c r="J7">
         <v>0</v>
-      </c>
-      <c r="H7">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>16.28</v>
       </c>
     </row>
   </sheetData>
@@ -4602,7 +4602,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4637,193 +4637,193 @@
         <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920252</v>
+        <v>21330051920261</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920252</v>
+        <v>21330051920261</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920252</v>
+        <v>21330051920261</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920252</v>
+        <v>21330051920262</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920253</v>
+        <v>21330051920265</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" t="s">
         <v>93</v>
       </c>
-      <c r="D7" t="s">
-        <v>110</v>
-      </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920257</v>
+        <v>21330051920265</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920261</v>
+        <v>21330051920269</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920261</v>
+        <v>21330051920269</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920261</v>
+        <v>21330051920273</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" t="s">
         <v>95</v>
       </c>
-      <c r="D11" t="s">
-        <v>112</v>
-      </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
         <v>68</v>
@@ -4831,1042 +4831,82 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920261</v>
+        <v>21330051920274</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920261</v>
+        <v>21330051920281</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920261</v>
+        <v>21330051920282</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920360</v>
+        <v>21330051920285</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920262</v>
-      </c>
-      <c r="B16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920262</v>
-      </c>
-      <c r="B17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920262</v>
-      </c>
-      <c r="B18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" t="s">
-        <v>114</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920262</v>
-      </c>
-      <c r="B19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" t="s">
-        <v>114</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920265</v>
-      </c>
-      <c r="B20" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" t="s">
-        <v>98</v>
-      </c>
-      <c r="D20" t="s">
-        <v>115</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920265</v>
-      </c>
-      <c r="B21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" t="s">
-        <v>115</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920265</v>
-      </c>
-      <c r="B22" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" t="s">
-        <v>115</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920265</v>
-      </c>
-      <c r="B23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" t="s">
-        <v>115</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920265</v>
-      </c>
-      <c r="B24" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" t="s">
-        <v>115</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920267</v>
-      </c>
-      <c r="B25" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" t="s">
-        <v>99</v>
-      </c>
-      <c r="D25" t="s">
-        <v>116</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920267</v>
-      </c>
-      <c r="B26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" t="s">
-        <v>99</v>
-      </c>
-      <c r="D26" t="s">
-        <v>116</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920267</v>
-      </c>
-      <c r="B27" t="s">
-        <v>80</v>
-      </c>
-      <c r="C27" t="s">
-        <v>99</v>
-      </c>
-      <c r="D27" t="s">
-        <v>116</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920267</v>
-      </c>
-      <c r="B28" t="s">
-        <v>80</v>
-      </c>
-      <c r="C28" t="s">
-        <v>99</v>
-      </c>
-      <c r="D28" t="s">
-        <v>116</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920267</v>
-      </c>
-      <c r="B29" t="s">
-        <v>80</v>
-      </c>
-      <c r="C29" t="s">
-        <v>99</v>
-      </c>
-      <c r="D29" t="s">
-        <v>116</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920358</v>
-      </c>
-      <c r="B30" t="s">
-        <v>81</v>
-      </c>
-      <c r="C30" t="s">
-        <v>100</v>
-      </c>
-      <c r="D30" t="s">
-        <v>117</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920358</v>
-      </c>
-      <c r="B31" t="s">
-        <v>81</v>
-      </c>
-      <c r="C31" t="s">
-        <v>100</v>
-      </c>
-      <c r="D31" t="s">
-        <v>117</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920269</v>
-      </c>
-      <c r="B32" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" t="s">
-        <v>101</v>
-      </c>
-      <c r="D32" t="s">
-        <v>118</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920269</v>
-      </c>
-      <c r="B33" t="s">
-        <v>82</v>
-      </c>
-      <c r="C33" t="s">
-        <v>101</v>
-      </c>
-      <c r="D33" t="s">
-        <v>118</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920269</v>
-      </c>
-      <c r="B34" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" t="s">
-        <v>101</v>
-      </c>
-      <c r="D34" t="s">
-        <v>118</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920269</v>
-      </c>
-      <c r="B35" t="s">
-        <v>82</v>
-      </c>
-      <c r="C35" t="s">
-        <v>101</v>
-      </c>
-      <c r="D35" t="s">
-        <v>118</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920271</v>
-      </c>
-      <c r="B36" t="s">
-        <v>83</v>
-      </c>
-      <c r="C36" t="s">
-        <v>102</v>
-      </c>
-      <c r="D36" t="s">
-        <v>119</v>
-      </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920273</v>
-      </c>
-      <c r="B37" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" t="s">
-        <v>103</v>
-      </c>
-      <c r="D37" t="s">
-        <v>120</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920273</v>
-      </c>
-      <c r="B38" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" t="s">
-        <v>103</v>
-      </c>
-      <c r="D38" t="s">
-        <v>120</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920273</v>
-      </c>
-      <c r="B39" t="s">
-        <v>84</v>
-      </c>
-      <c r="C39" t="s">
-        <v>103</v>
-      </c>
-      <c r="D39" t="s">
-        <v>120</v>
-      </c>
-      <c r="E39" t="s">
-        <v>6</v>
-      </c>
-      <c r="F39" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920273</v>
-      </c>
-      <c r="B40" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" t="s">
-        <v>103</v>
-      </c>
-      <c r="D40" t="s">
-        <v>120</v>
-      </c>
-      <c r="E40" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920273</v>
-      </c>
-      <c r="B41" t="s">
-        <v>84</v>
-      </c>
-      <c r="C41" t="s">
-        <v>103</v>
-      </c>
-      <c r="D41" t="s">
-        <v>120</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920274</v>
-      </c>
-      <c r="B42" t="s">
-        <v>85</v>
-      </c>
-      <c r="C42" t="s">
-        <v>77</v>
-      </c>
-      <c r="D42" t="s">
-        <v>121</v>
-      </c>
-      <c r="E42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920274</v>
-      </c>
-      <c r="B43" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43" t="s">
-        <v>77</v>
-      </c>
-      <c r="D43" t="s">
-        <v>121</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920274</v>
-      </c>
-      <c r="B44" t="s">
-        <v>85</v>
-      </c>
-      <c r="C44" t="s">
-        <v>77</v>
-      </c>
-      <c r="D44" t="s">
-        <v>121</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920274</v>
-      </c>
-      <c r="B45" t="s">
-        <v>85</v>
-      </c>
-      <c r="C45" t="s">
-        <v>77</v>
-      </c>
-      <c r="D45" t="s">
-        <v>121</v>
-      </c>
-      <c r="E45" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920277</v>
-      </c>
-      <c r="B46" t="s">
-        <v>86</v>
-      </c>
-      <c r="C46" t="s">
-        <v>104</v>
-      </c>
-      <c r="D46" t="s">
-        <v>122</v>
-      </c>
-      <c r="E46" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920277</v>
-      </c>
-      <c r="B47" t="s">
-        <v>86</v>
-      </c>
-      <c r="C47" t="s">
-        <v>104</v>
-      </c>
-      <c r="D47" t="s">
-        <v>122</v>
-      </c>
-      <c r="E47" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920281</v>
-      </c>
-      <c r="B48" t="s">
-        <v>87</v>
-      </c>
-      <c r="C48" t="s">
-        <v>84</v>
-      </c>
-      <c r="D48" t="s">
-        <v>123</v>
-      </c>
-      <c r="E48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920281</v>
-      </c>
-      <c r="B49" t="s">
-        <v>87</v>
-      </c>
-      <c r="C49" t="s">
-        <v>84</v>
-      </c>
-      <c r="D49" t="s">
-        <v>123</v>
-      </c>
-      <c r="E49" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920281</v>
-      </c>
-      <c r="B50" t="s">
-        <v>87</v>
-      </c>
-      <c r="C50" t="s">
-        <v>84</v>
-      </c>
-      <c r="D50" t="s">
-        <v>123</v>
-      </c>
-      <c r="E50" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>21330051920281</v>
-      </c>
-      <c r="B51" t="s">
-        <v>87</v>
-      </c>
-      <c r="C51" t="s">
-        <v>84</v>
-      </c>
-      <c r="D51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E51" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920282</v>
-      </c>
-      <c r="B52" t="s">
-        <v>88</v>
-      </c>
-      <c r="C52" t="s">
-        <v>105</v>
-      </c>
-      <c r="D52" t="s">
-        <v>124</v>
-      </c>
-      <c r="E52" t="s">
-        <v>7</v>
-      </c>
-      <c r="F52" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920282</v>
-      </c>
-      <c r="B53" t="s">
-        <v>88</v>
-      </c>
-      <c r="C53" t="s">
-        <v>105</v>
-      </c>
-      <c r="D53" t="s">
-        <v>124</v>
-      </c>
-      <c r="E53" t="s">
-        <v>6</v>
-      </c>
-      <c r="F53" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920282</v>
-      </c>
-      <c r="B54" t="s">
-        <v>88</v>
-      </c>
-      <c r="C54" t="s">
-        <v>105</v>
-      </c>
-      <c r="D54" t="s">
-        <v>124</v>
-      </c>
-      <c r="E54" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920282</v>
-      </c>
-      <c r="B55" t="s">
-        <v>88</v>
-      </c>
-      <c r="C55" t="s">
-        <v>105</v>
-      </c>
-      <c r="D55" t="s">
-        <v>124</v>
-      </c>
-      <c r="E55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F55" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>21330051920283</v>
-      </c>
-      <c r="B56" t="s">
-        <v>89</v>
-      </c>
-      <c r="C56" t="s">
-        <v>106</v>
-      </c>
-      <c r="D56" t="s">
-        <v>125</v>
-      </c>
-      <c r="E56" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>21330051920284</v>
-      </c>
-      <c r="B57" t="s">
-        <v>90</v>
-      </c>
-      <c r="C57" t="s">
-        <v>107</v>
-      </c>
-      <c r="D57" t="s">
-        <v>126</v>
-      </c>
-      <c r="E57" t="s">
-        <v>7</v>
-      </c>
-      <c r="F57" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>21330051920284</v>
-      </c>
-      <c r="B58" t="s">
-        <v>90</v>
-      </c>
-      <c r="C58" t="s">
-        <v>107</v>
-      </c>
-      <c r="D58" t="s">
-        <v>126</v>
-      </c>
-      <c r="E58" t="s">
-        <v>10</v>
-      </c>
-      <c r="F58" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>21330051920285</v>
-      </c>
-      <c r="B59" t="s">
-        <v>91</v>
-      </c>
-      <c r="C59" t="s">
-        <v>84</v>
-      </c>
-      <c r="D59" t="s">
-        <v>127</v>
-      </c>
-      <c r="E59" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>21330051920285</v>
-      </c>
-      <c r="B60" t="s">
-        <v>91</v>
-      </c>
-      <c r="C60" t="s">
-        <v>84</v>
-      </c>
-      <c r="D60" t="s">
-        <v>127</v>
-      </c>
-      <c r="E60" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>21330051920285</v>
-      </c>
-      <c r="B61" t="s">
-        <v>91</v>
-      </c>
-      <c r="C61" t="s">
-        <v>84</v>
-      </c>
-      <c r="D61" t="s">
-        <v>127</v>
-      </c>
-      <c r="E61" t="s">
-        <v>10</v>
-      </c>
-      <c r="F61" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>21330051920285</v>
-      </c>
-      <c r="B62" t="s">
-        <v>91</v>
-      </c>
-      <c r="C62" t="s">
-        <v>84</v>
-      </c>
-      <c r="D62" t="s">
-        <v>127</v>
-      </c>
-      <c r="E62" t="s">
-        <v>9</v>
-      </c>
-      <c r="F62" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>21330051920288</v>
-      </c>
-      <c r="B63" t="s">
-        <v>92</v>
-      </c>
-      <c r="C63" t="s">
-        <v>108</v>
-      </c>
-      <c r="D63" t="s">
-        <v>128</v>
-      </c>
-      <c r="E63" t="s">
-        <v>10</v>
-      </c>
-      <c r="F63" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -5905,254 +4945,254 @@
         <v>21330051920261</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920252</v>
+        <v>21330051920265</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920265</v>
+        <v>21330051920269</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920267</v>
+        <v>21330051920252</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920273</v>
+        <v>21330051920262</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920262</v>
+        <v>21330051920273</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920269</v>
+        <v>21330051920274</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920274</v>
+        <v>21330051920281</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920281</v>
+        <v>21330051920282</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920282</v>
+        <v>21330051920285</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920285</v>
+        <v>21330051920251</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920358</v>
+        <v>21330051920253</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920277</v>
+        <v>21330051920254</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920284</v>
+        <v>21330051920255</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920253</v>
+        <v>21330051920256</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -6160,98 +5200,98 @@
         <v>21330051920257</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>154</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920360</v>
+        <v>21330051920258</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920271</v>
+        <v>21330051920259</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920283</v>
+        <v>21330051920260</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="D20" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920288</v>
+        <v>21330051920360</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="D21" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920251</v>
+        <v>21330051920263</v>
       </c>
       <c r="B22" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="D22" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -6259,16 +5299,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920254</v>
+        <v>21330051920264</v>
       </c>
       <c r="B23" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6276,16 +5316,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920255</v>
+        <v>21330051920266</v>
       </c>
       <c r="B24" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -6293,16 +5333,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920256</v>
+        <v>21330051920267</v>
       </c>
       <c r="B25" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="D25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -6310,16 +5350,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920258</v>
+        <v>21330051920358</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="C26" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="D26" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -6327,16 +5367,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920259</v>
+        <v>21330051920268</v>
       </c>
       <c r="B27" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="C27" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="D27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -6344,16 +5384,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920260</v>
+        <v>21330051920270</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="C28" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="D28" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -6361,16 +5401,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920263</v>
+        <v>21330051920271</v>
       </c>
       <c r="B29" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="C29" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="D29" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -6378,13 +5418,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920264</v>
+        <v>21330051920272</v>
       </c>
       <c r="B30" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="D30" t="s">
         <v>166</v>
@@ -6395,13 +5435,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920266</v>
+        <v>21330051920361</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D31" t="s">
         <v>167</v>
@@ -6412,13 +5452,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920268</v>
+        <v>21330051920275</v>
       </c>
       <c r="B32" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="C32" t="s">
-        <v>152</v>
+        <v>84</v>
       </c>
       <c r="D32" t="s">
         <v>168</v>
@@ -6429,13 +5469,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920270</v>
+        <v>21330051920362</v>
       </c>
       <c r="B33" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="D33" t="s">
         <v>169</v>
@@ -6446,13 +5486,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920272</v>
+        <v>21330051920276</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C34" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="D34" t="s">
         <v>170</v>
@@ -6463,13 +5503,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920361</v>
+        <v>21330051920277</v>
       </c>
       <c r="B35" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="C35" t="s">
-        <v>95</v>
+        <v>143</v>
       </c>
       <c r="D35" t="s">
         <v>171</v>
@@ -6480,13 +5520,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920275</v>
+        <v>21330051920278</v>
       </c>
       <c r="B36" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="C36" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D36" t="s">
         <v>172</v>
@@ -6497,13 +5537,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920362</v>
+        <v>21330051920279</v>
       </c>
       <c r="B37" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="C37" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D37" t="s">
         <v>173</v>
@@ -6514,13 +5554,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920276</v>
+        <v>21330051920280</v>
       </c>
       <c r="B38" t="s">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="C38" t="s">
-        <v>155</v>
+        <v>105</v>
       </c>
       <c r="D38" t="s">
         <v>174</v>
@@ -6531,13 +5571,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920278</v>
+        <v>21330051920283</v>
       </c>
       <c r="B39" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="C39" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="D39" t="s">
         <v>175</v>
@@ -6548,13 +5588,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>21330051920279</v>
+        <v>21330051920284</v>
       </c>
       <c r="B40" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="D40" t="s">
         <v>176</v>
@@ -6565,13 +5605,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>21330051920280</v>
+        <v>21330051920286</v>
       </c>
       <c r="B41" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="C41" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D41" t="s">
         <v>177</v>
@@ -6582,13 +5622,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>21330051920286</v>
+        <v>20330051920358</v>
       </c>
       <c r="B42" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
-        <v>101</v>
+        <v>146</v>
       </c>
       <c r="D42" t="s">
         <v>178</v>
@@ -6599,13 +5639,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>20330051920358</v>
+        <v>21330051920287</v>
       </c>
       <c r="B43" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C43" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D43" t="s">
         <v>179</v>
@@ -6616,13 +5656,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>21330051920287</v>
+        <v>21330051920288</v>
       </c>
       <c r="B44" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="C44" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D44" t="s">
         <v>180</v>
@@ -6638,7 +5678,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6670,108 +5710,108 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920358</v>
+        <v>21330051920284</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>176</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920358</v>
+        <v>21330051920284</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>176</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920277</v>
+        <v>21330051920288</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>180</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920277</v>
+        <v>21330051920288</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
+        <v>180</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920284</v>
+        <v>21330051920253</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -6780,27 +5820,27 @@
         <v>64</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920284</v>
+        <v>21330051920262</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -6808,22 +5848,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920288</v>
+        <v>21330051920271</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6831,16 +5871,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920288</v>
+        <v>21330051920277</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
+        <v>171</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -6849,122 +5889,7 @@
         <v>65</v>
       </c>
       <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920253</v>
-      </c>
-      <c r="B10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10" t="s">
-        <v>110</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920257</v>
-      </c>
-      <c r="B11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" t="s">
-        <v>111</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920360</v>
-      </c>
-      <c r="B12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920271</v>
-      </c>
-      <c r="B13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" t="s">
-        <v>102</v>
-      </c>
-      <c r="D13" t="s">
-        <v>119</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>65</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920283</v>
-      </c>
-      <c r="B14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" t="s">
-        <v>106</v>
-      </c>
-      <c r="D14" t="s">
-        <v>125</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>66</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/1DM - Estadisticos 20211.xlsx
+++ b/grupos/1DM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="181">
   <si>
     <t>Materia</t>
   </si>
@@ -248,253 +248,253 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ONOFRE</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>TERCERO</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>NAVA</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>MELANI PAOLA</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>RICARDO ABEL</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>MARIANA PAOLA</t>
+  </si>
+  <si>
+    <t>ANGELICA NAOMI</t>
+  </si>
+  <si>
+    <t>CARLOS ROBERTO</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>ARGÜELLO</t>
+  </si>
+  <si>
+    <t>CRESCENCIO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
     <t>HIDALGO</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ONOFRE</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>TERCERO</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MADRAZO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>PATIÑO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VENEGAS</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>NARANJO</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>PETRILLI</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
   </si>
   <si>
     <t>ARCADIO</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>NAVA</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>MELANI PAOLA</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>BENITO</t>
+  </si>
+  <si>
+    <t>APONTE</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>ARAUZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>AMECA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>YARELI</t>
+  </si>
+  <si>
+    <t>ATZIN HEFZIBA</t>
+  </si>
+  <si>
+    <t>NADIA</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>SUGHEYDI JAZMIN</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>EMILIANO</t>
+  </si>
+  <si>
+    <t>LESLY JAREDT</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
+    <t>ANGEL SAMUEL</t>
   </si>
   <si>
     <t>ANA LILIANA</t>
-  </si>
-  <si>
-    <t>RICARDO ABEL</t>
-  </si>
-  <si>
-    <t>LUIS ARMANDO</t>
-  </si>
-  <si>
-    <t>MARIANA PAOLA</t>
-  </si>
-  <si>
-    <t>ANGELICA NAOMI</t>
-  </si>
-  <si>
-    <t>CARLOS ROBERTO</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>ARGÜELLO</t>
-  </si>
-  <si>
-    <t>CRESCENCIO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MADRAZO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>PATIÑO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>NARANJO</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>PETRILLI</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>BENITO</t>
-  </si>
-  <si>
-    <t>APONTE</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>ARAUZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>AMECA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>YARELI</t>
-  </si>
-  <si>
-    <t>ATZIN HEFZIBA</t>
-  </si>
-  <si>
-    <t>NADIA</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>SUGHEYDI JAZMIN</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>EMILIANO</t>
-  </si>
-  <si>
-    <t>LESLY JAREDT</t>
-  </si>
-  <si>
-    <t>MARIA TERESA</t>
-  </si>
-  <si>
-    <t>ANGEL SAMUEL</t>
   </si>
   <si>
     <t>VENUS</t>
@@ -1064,7 +1064,7 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>8</v>
@@ -1141,7 +1141,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I5">
         <v>6</v>
@@ -1218,7 +1218,7 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>7</v>
@@ -1295,7 +1295,7 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>9</v>
@@ -1331,7 +1331,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U7">
         <v>10</v>
@@ -1372,7 +1372,7 @@
         <v>7</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>8</v>
@@ -1449,7 +1449,7 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I9">
         <v>6</v>
@@ -1485,7 +1485,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>8</v>
@@ -1526,7 +1526,7 @@
         <v>7</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
         <v>8</v>
@@ -1603,7 +1603,7 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
         <v>7</v>
@@ -1680,7 +1680,7 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
         <v>8</v>
@@ -1757,7 +1757,7 @@
         <v>7</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
         <v>9</v>
@@ -1834,7 +1834,7 @@
         <v>7</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <v>7</v>
@@ -1870,7 +1870,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -1893,7 +1893,7 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C15">
         <v>-1</v>
@@ -1911,7 +1911,7 @@
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1947,7 +1947,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U15">
         <v>-1</v>
@@ -1988,7 +1988,7 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
         <v>7</v>
@@ -2047,7 +2047,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C17">
         <v>8</v>
@@ -2065,7 +2065,7 @@
         <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I17">
         <v>7</v>
@@ -2101,7 +2101,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>8</v>
@@ -2142,7 +2142,7 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
         <v>7</v>
@@ -2178,7 +2178,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>8</v>
@@ -2219,7 +2219,7 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2296,7 +2296,7 @@
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2373,7 +2373,7 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I21">
         <v>7</v>
@@ -2409,7 +2409,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>8</v>
@@ -2450,7 +2450,7 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I22">
         <v>7</v>
@@ -2486,7 +2486,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2527,7 +2527,7 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
         <v>8</v>
@@ -2604,7 +2604,7 @@
         <v>-1</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2681,7 +2681,7 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
         <v>9</v>
@@ -2758,7 +2758,7 @@
         <v>5</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I26">
         <v>10</v>
@@ -2835,7 +2835,7 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
         <v>9</v>
@@ -2871,7 +2871,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U27">
         <v>9</v>
@@ -2912,7 +2912,7 @@
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -2989,7 +2989,7 @@
         <v>5</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -3025,7 +3025,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U29">
         <v>8</v>
@@ -3066,7 +3066,7 @@
         <v>6</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I30">
         <v>8</v>
@@ -3143,7 +3143,7 @@
         <v>7</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <v>8</v>
@@ -3179,7 +3179,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U31">
         <v>9</v>
@@ -3220,7 +3220,7 @@
         <v>6</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I32">
         <v>9</v>
@@ -3256,7 +3256,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U32">
         <v>10</v>
@@ -3297,7 +3297,7 @@
         <v>8</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
         <v>9</v>
@@ -3333,7 +3333,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U33">
         <v>9</v>
@@ -3374,7 +3374,7 @@
         <v>5</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I34">
         <v>8</v>
@@ -3451,7 +3451,7 @@
         <v>7</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I35">
         <v>9</v>
@@ -3528,7 +3528,7 @@
         <v>6</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I36">
         <v>10</v>
@@ -3605,7 +3605,7 @@
         <v>7</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I37">
         <v>10</v>
@@ -3641,7 +3641,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U37">
         <v>10</v>
@@ -3682,7 +3682,7 @@
         <v>6</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I38">
         <v>6</v>
@@ -3718,7 +3718,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U38">
         <v>7</v>
@@ -3759,7 +3759,7 @@
         <v>5</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I39">
         <v>-1</v>
@@ -3795,7 +3795,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U39">
         <v>-1</v>
@@ -3836,7 +3836,7 @@
         <v>5</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I40">
         <v>6</v>
@@ -3913,7 +3913,7 @@
         <v>5</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I41">
         <v>6</v>
@@ -3990,7 +3990,7 @@
         <v>7</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I42">
         <v>9</v>
@@ -4067,7 +4067,7 @@
         <v>5</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I43">
         <v>7</v>
@@ -4144,7 +4144,7 @@
         <v>6</v>
       </c>
       <c r="H44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I44">
         <v>6</v>
@@ -4221,7 +4221,7 @@
         <v>6</v>
       </c>
       <c r="H45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I45">
         <v>6</v>
@@ -4298,7 +4298,7 @@
         <v>6</v>
       </c>
       <c r="H46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I46">
         <v>7</v>
@@ -4481,22 +4481,22 @@
         <v>34</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4">
         <v>79.06999999999999</v>
       </c>
       <c r="G4">
-        <v>16.28</v>
+        <v>20.93</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>4.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4602,7 +4602,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4640,7 +4640,7 @@
         <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4657,10 +4657,10 @@
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4677,70 +4677,70 @@
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920261</v>
+        <v>21330051920265</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
         <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920262</v>
+        <v>21330051920265</v>
       </c>
       <c r="B6" t="s">
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920265</v>
+        <v>21330051920269</v>
       </c>
       <c r="B7" t="s">
         <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4751,161 +4751,121 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920265</v>
+        <v>21330051920269</v>
       </c>
       <c r="B8" t="s">
         <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920269</v>
+        <v>21330051920273</v>
       </c>
       <c r="B9" t="s">
         <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920269</v>
+        <v>21330051920274</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920273</v>
+        <v>21330051920281</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920274</v>
+        <v>21330051920282</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920281</v>
+        <v>21330051920285</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920282</v>
-      </c>
-      <c r="B14" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" t="s">
-        <v>98</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920285</v>
-      </c>
-      <c r="B15" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" t="s">
-        <v>99</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4948,13 +4908,13 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4962,13 +4922,13 @@
         <v>21330051920265</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -4979,13 +4939,13 @@
         <v>21330051920269</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -5002,7 +4962,7 @@
         <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -5010,13 +4970,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920262</v>
+        <v>21330051920273</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
         <v>92</v>
@@ -5027,16 +4987,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920273</v>
+        <v>21330051920274</v>
       </c>
       <c r="B7" t="s">
         <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -5044,16 +5004,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920274</v>
+        <v>21330051920281</v>
       </c>
       <c r="B8" t="s">
         <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -5061,16 +5021,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920281</v>
+        <v>21330051920282</v>
       </c>
       <c r="B9" t="s">
         <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5078,16 +5038,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920282</v>
+        <v>21330051920285</v>
       </c>
       <c r="B10" t="s">
         <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -5095,30 +5055,30 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920285</v>
+        <v>21330051920251</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920251</v>
+        <v>21330051920253</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D12" t="s">
         <v>149</v>
@@ -5129,13 +5089,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920253</v>
+        <v>21330051920254</v>
       </c>
       <c r="B13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D13" t="s">
         <v>150</v>
@@ -5146,13 +5106,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920254</v>
+        <v>21330051920255</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
         <v>151</v>
@@ -5163,13 +5123,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920255</v>
+        <v>21330051920256</v>
       </c>
       <c r="B15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="D15" t="s">
         <v>152</v>
@@ -5180,13 +5140,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920256</v>
+        <v>21330051920257</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D16" t="s">
         <v>153</v>
@@ -5197,13 +5157,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920257</v>
+        <v>21330051920258</v>
       </c>
       <c r="B17" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D17" t="s">
         <v>154</v>
@@ -5214,13 +5174,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920258</v>
+        <v>21330051920259</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
         <v>155</v>
@@ -5231,13 +5191,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920259</v>
+        <v>21330051920260</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="D19" t="s">
         <v>156</v>
@@ -5248,13 +5208,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920260</v>
+        <v>21330051920360</v>
       </c>
       <c r="B20" t="s">
         <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D20" t="s">
         <v>157</v>
@@ -5265,13 +5225,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920360</v>
+        <v>21330051920262</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D21" t="s">
         <v>158</v>
@@ -5285,13 +5245,13 @@
         <v>21330051920263</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -5302,10 +5262,10 @@
         <v>21330051920264</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C23" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D23" t="s">
         <v>159</v>
@@ -5319,7 +5279,7 @@
         <v>21330051920266</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
         <v>75</v>
@@ -5336,10 +5296,10 @@
         <v>21330051920267</v>
       </c>
       <c r="B25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D25" t="s">
         <v>161</v>
@@ -5353,10 +5313,10 @@
         <v>21330051920358</v>
       </c>
       <c r="B26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C26" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D26" t="s">
         <v>162</v>
@@ -5370,10 +5330,10 @@
         <v>21330051920268</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D27" t="s">
         <v>163</v>
@@ -5387,10 +5347,10 @@
         <v>21330051920270</v>
       </c>
       <c r="B28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C28" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D28" t="s">
         <v>164</v>
@@ -5404,10 +5364,10 @@
         <v>21330051920271</v>
       </c>
       <c r="B29" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D29" t="s">
         <v>165</v>
@@ -5421,10 +5381,10 @@
         <v>21330051920272</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D30" t="s">
         <v>166</v>
@@ -5438,10 +5398,10 @@
         <v>21330051920361</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D31" t="s">
         <v>167</v>
@@ -5455,10 +5415,10 @@
         <v>21330051920275</v>
       </c>
       <c r="B32" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D32" t="s">
         <v>168</v>
@@ -5472,10 +5432,10 @@
         <v>21330051920362</v>
       </c>
       <c r="B33" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C33" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D33" t="s">
         <v>169</v>
@@ -5489,10 +5449,10 @@
         <v>21330051920276</v>
       </c>
       <c r="B34" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C34" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D34" t="s">
         <v>170</v>
@@ -5506,10 +5466,10 @@
         <v>21330051920277</v>
       </c>
       <c r="B35" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C35" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D35" t="s">
         <v>171</v>
@@ -5523,10 +5483,10 @@
         <v>21330051920278</v>
       </c>
       <c r="B36" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C36" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D36" t="s">
         <v>172</v>
@@ -5540,10 +5500,10 @@
         <v>21330051920279</v>
       </c>
       <c r="B37" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C37" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D37" t="s">
         <v>173</v>
@@ -5557,10 +5517,10 @@
         <v>21330051920280</v>
       </c>
       <c r="B38" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C38" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D38" t="s">
         <v>174</v>
@@ -5574,10 +5534,10 @@
         <v>21330051920283</v>
       </c>
       <c r="B39" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C39" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D39" t="s">
         <v>175</v>
@@ -5591,10 +5551,10 @@
         <v>21330051920284</v>
       </c>
       <c r="B40" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C40" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D40" t="s">
         <v>176</v>
@@ -5608,10 +5568,10 @@
         <v>21330051920286</v>
       </c>
       <c r="B41" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C41" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D41" t="s">
         <v>177</v>
@@ -5625,10 +5585,10 @@
         <v>20330051920358</v>
       </c>
       <c r="B42" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C42" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D42" t="s">
         <v>178</v>
@@ -5642,10 +5602,10 @@
         <v>21330051920287</v>
       </c>
       <c r="B43" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C43" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D43" t="s">
         <v>179</v>
@@ -5659,10 +5619,10 @@
         <v>21330051920288</v>
       </c>
       <c r="B44" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C44" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D44" t="s">
         <v>180</v>
@@ -5678,7 +5638,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5713,10 +5673,10 @@
         <v>21330051920284</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D2" t="s">
         <v>176</v>
@@ -5736,10 +5696,10 @@
         <v>21330051920284</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D3" t="s">
         <v>176</v>
@@ -5759,10 +5719,10 @@
         <v>21330051920288</v>
       </c>
       <c r="B4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D4" t="s">
         <v>180</v>
@@ -5782,10 +5742,10 @@
         <v>21330051920288</v>
       </c>
       <c r="B5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D5" t="s">
         <v>180</v>
@@ -5805,13 +5765,13 @@
         <v>21330051920253</v>
       </c>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5825,39 +5785,39 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920262</v>
+        <v>21330051920271</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>138</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>165</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920271</v>
+        <v>21330051920277</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D8" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -5866,29 +5826,6 @@
         <v>65</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920277</v>
-      </c>
-      <c r="B9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9" t="s">
-        <v>143</v>
-      </c>
-      <c r="D9" t="s">
-        <v>171</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DM - Estadisticos 20211.xlsx
+++ b/grupos/1DM - Estadisticos 20211.xlsx
@@ -1615,7 +1615,7 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>7</v>
@@ -1769,7 +1769,7 @@
         <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>7</v>
@@ -2154,7 +2154,7 @@
         <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2308,7 +2308,7 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2616,7 +2616,7 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -3001,7 +3001,7 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -3386,7 +3386,7 @@
         <v>9</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M34">
         <v>6</v>
@@ -3848,7 +3848,7 @@
         <v>-1</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M40">
         <v>-1</v>

--- a/grupos/1DM - Estadisticos 20211.xlsx
+++ b/grupos/1DM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="181">
   <si>
     <t>Materia</t>
   </si>
@@ -212,10 +212,13 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>González Altamirano Victorino Juventino</t>
+    <t>Morales Vallejo Jorge Luis</t>
   </si>
   <si>
     <t>Rosas Aguilar Claudia Leonor</t>
@@ -224,9 +227,6 @@
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
-    <t>Morales Vallejo Jorge Luis</t>
-  </si>
-  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
@@ -242,313 +242,313 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
     <t>ALDUCIN</t>
   </si>
   <si>
+    <t>ARGÜELLO</t>
+  </si>
+  <si>
+    <t>CRESCENCIO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>HIDALGO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MADRAZO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
     <t>ONOFRE</t>
   </si>
   <si>
+    <t>PATIÑO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
     <t>REYES</t>
   </si>
   <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>TLAXCALA</t>
   </si>
   <si>
     <t>TERCERO</t>
   </si>
   <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>VALLEJO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VENEGAS</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>NARANJO</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>PETRILLI</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>ARCADIO</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>BENITO</t>
+  </si>
+  <si>
+    <t>APONTE</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
   </si>
   <si>
     <t>NAVA</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>ARAUZ</t>
+  </si>
+  <si>
     <t>CARRILLO</t>
   </si>
   <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>AMECA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>YARELI</t>
+  </si>
+  <si>
     <t>MELANI PAOLA</t>
   </si>
   <si>
+    <t>ATZIN HEFZIBA</t>
+  </si>
+  <si>
+    <t>NADIA</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>SUGHEYDI JAZMIN</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>EMILIANO</t>
+  </si>
+  <si>
+    <t>LESLY JAREDT</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
     <t>ABIGAIL</t>
   </si>
   <si>
+    <t>ANGEL SAMUEL</t>
+  </si>
+  <si>
+    <t>ANA LILIANA</t>
+  </si>
+  <si>
+    <t>VENUS</t>
+  </si>
+  <si>
     <t>RICARDO ABEL</t>
   </si>
   <si>
+    <t>BIBIAN YANEL</t>
+  </si>
+  <si>
+    <t>ANGELO RENE</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>DULCE NAOMI</t>
+  </si>
+  <si>
     <t>LUIS ARMANDO</t>
   </si>
   <si>
+    <t>ALYN</t>
+  </si>
+  <si>
+    <t>NATALIA</t>
+  </si>
+  <si>
+    <t>MILDRED MARIANA</t>
+  </si>
+  <si>
     <t>MARIANA PAOLA</t>
   </si>
   <si>
     <t>ANGELICA NAOMI</t>
   </si>
   <si>
+    <t>DUILIO</t>
+  </si>
+  <si>
+    <t>VIRIDIANA</t>
+  </si>
+  <si>
+    <t>JAQUELINE</t>
+  </si>
+  <si>
+    <t>JOSE ANGEL</t>
+  </si>
+  <si>
+    <t>BRYAN ABRAHAM</t>
+  </si>
+  <si>
+    <t>ARANTXA</t>
+  </si>
+  <si>
+    <t>ISAI</t>
+  </si>
+  <si>
+    <t>BETHSABE</t>
+  </si>
+  <si>
     <t>CARLOS ROBERTO</t>
   </si>
   <si>
     <t>MARIA DEL CARMEN</t>
   </si>
   <si>
+    <t>VIANEY</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
     <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>ARGÜELLO</t>
-  </si>
-  <si>
-    <t>CRESCENCIO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>HIDALGO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MADRAZO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>PATIÑO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>NARANJO</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>PETRILLI</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>ARCADIO</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>BENITO</t>
-  </si>
-  <si>
-    <t>APONTE</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>ARAUZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>AMECA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>YARELI</t>
-  </si>
-  <si>
-    <t>ATZIN HEFZIBA</t>
-  </si>
-  <si>
-    <t>NADIA</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>SUGHEYDI JAZMIN</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>EMILIANO</t>
-  </si>
-  <si>
-    <t>LESLY JAREDT</t>
-  </si>
-  <si>
-    <t>MARIA TERESA</t>
-  </si>
-  <si>
-    <t>ANGEL SAMUEL</t>
-  </si>
-  <si>
-    <t>ANA LILIANA</t>
-  </si>
-  <si>
-    <t>VENUS</t>
-  </si>
-  <si>
-    <t>BIBIAN YANEL</t>
-  </si>
-  <si>
-    <t>ANGELO RENE</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>DULCE NAOMI</t>
-  </si>
-  <si>
-    <t>ALYN</t>
-  </si>
-  <si>
-    <t>NATALIA</t>
-  </si>
-  <si>
-    <t>MILDRED MARIANA</t>
-  </si>
-  <si>
-    <t>DUILIO</t>
-  </si>
-  <si>
-    <t>VIRIDIANA</t>
-  </si>
-  <si>
-    <t>JAQUELINE</t>
-  </si>
-  <si>
-    <t>JOSE ANGEL</t>
-  </si>
-  <si>
-    <t>BRYAN ABRAHAM</t>
-  </si>
-  <si>
-    <t>ARANTXA</t>
-  </si>
-  <si>
-    <t>ISAI</t>
-  </si>
-  <si>
-    <t>BETHSABE</t>
-  </si>
-  <si>
-    <t>VIANEY</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
   </si>
   <si>
     <t>MAGDA SARAY</t>
@@ -1082,22 +1082,22 @@
         <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
         <v>9</v>
@@ -1106,16 +1106,16 @@
         <v>9</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1132,7 +1132,7 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F5">
         <v>6</v>
@@ -1150,34 +1150,34 @@
         <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U5">
         <v>5</v>
@@ -1186,7 +1186,7 @@
         <v>5</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>6</v>
@@ -1236,22 +1236,22 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -1260,7 +1260,7 @@
         <v>7</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -1313,22 +1313,22 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1390,22 +1390,22 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1420,10 +1420,10 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1467,37 +1467,37 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
         <v>7</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>7</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1544,28 +1544,28 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>8</v>
       </c>
       <c r="U10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>8</v>
@@ -1612,7 +1612,7 @@
         <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>6</v>
@@ -1621,40 +1621,40 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>8</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>6</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1698,37 +1698,37 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>9</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>10</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>8</v>
@@ -1775,34 +1775,34 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>6</v>
@@ -1852,40 +1852,40 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>8</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>8</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1896,13 +1896,13 @@
         <v>5</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>5</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F15">
         <v>6</v>
@@ -1914,49 +1914,49 @@
         <v>5</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
         <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
         <v>5</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X15">
         <v>6</v>
@@ -1997,7 +1997,7 @@
         <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>7</v>
@@ -2006,37 +2006,37 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>6</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -2080,28 +2080,28 @@
         <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>8</v>
@@ -2110,13 +2110,13 @@
         <v>6</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2157,25 +2157,25 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T18">
         <v>7</v>
@@ -2187,7 +2187,7 @@
         <v>7</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>6</v>
@@ -2222,7 +2222,7 @@
         <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>7</v>
@@ -2237,28 +2237,28 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
         <v>7</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>6</v>
@@ -2267,7 +2267,7 @@
         <v>6</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -2281,13 +2281,13 @@
         <v>5</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>5</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -2299,49 +2299,49 @@
         <v>5</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
         <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
         <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
         <v>5</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X20">
         <v>5</v>
@@ -2391,22 +2391,22 @@
         <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>7</v>
@@ -2418,7 +2418,7 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2468,22 +2468,22 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
         <v>7</v>
@@ -2492,13 +2492,13 @@
         <v>7</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y22">
         <v>6</v>
@@ -2545,25 +2545,25 @@
         <v>7</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>9</v>
@@ -2595,67 +2595,67 @@
         <v>5</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F24">
         <v>5</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H24">
         <v>5</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
         <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>5</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
         <v>5</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>5</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X24">
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2699,22 +2699,22 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2723,7 +2723,7 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2776,22 +2776,22 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>9</v>
@@ -2806,10 +2806,10 @@
         <v>10</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2853,22 +2853,22 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2877,7 +2877,7 @@
         <v>9</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -2897,7 +2897,7 @@
         <v>5</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D28">
         <v>5</v>
@@ -2915,46 +2915,46 @@
         <v>5</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
         <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
         <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T28">
         <v>5</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>8</v>
@@ -2980,7 +2980,7 @@
         <v>5</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F29">
         <v>5</v>
@@ -2992,52 +2992,52 @@
         <v>5</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
         <v>5</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L29">
         <v>5</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T29">
         <v>5</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V29">
         <v>5</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y29">
         <v>5</v>
@@ -3084,31 +3084,31 @@
         <v>6</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3161,22 +3161,22 @@
         <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -3188,7 +3188,7 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>9</v>
@@ -3238,40 +3238,40 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3315,28 +3315,28 @@
         <v>7</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V33">
         <v>8</v>
@@ -3392,22 +3392,22 @@
         <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
         <v>6</v>
@@ -3416,16 +3416,16 @@
         <v>7</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X34">
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3469,40 +3469,40 @@
         <v>6</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>10</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y35">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3546,31 +3546,31 @@
         <v>8</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U36">
         <v>10</v>
       </c>
       <c r="V36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W36">
         <v>9</v>
@@ -3623,22 +3623,22 @@
         <v>9</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T37">
         <v>10</v>
@@ -3697,25 +3697,25 @@
         <v>8</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T38">
         <v>8</v>
@@ -3724,7 +3724,7 @@
         <v>7</v>
       </c>
       <c r="V38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W38">
         <v>8</v>
@@ -3744,7 +3744,7 @@
         <v>7</v>
       </c>
       <c r="C39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D39">
         <v>5</v>
@@ -3762,52 +3762,52 @@
         <v>5</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J39">
         <v>5</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L39">
         <v>7</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V39">
         <v>5</v>
       </c>
       <c r="W39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y39">
         <v>5</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="E40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F40">
         <v>5</v>
@@ -3845,43 +3845,43 @@
         <v>5</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L40">
         <v>5</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T40">
         <v>5</v>
       </c>
       <c r="U40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V40">
         <v>5</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X40">
         <v>5</v>
@@ -3904,7 +3904,7 @@
         <v>5</v>
       </c>
       <c r="E41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F41">
         <v>6</v>
@@ -3922,43 +3922,43 @@
         <v>5</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L41">
         <v>6</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V41">
         <v>5</v>
       </c>
       <c r="W41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X41">
         <v>6</v>
@@ -4008,37 +4008,37 @@
         <v>6</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U42">
         <v>9</v>
       </c>
       <c r="V42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y42">
         <v>7</v>
@@ -4085,22 +4085,22 @@
         <v>6</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T43">
         <v>6</v>
@@ -4109,16 +4109,16 @@
         <v>7</v>
       </c>
       <c r="V43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W43">
         <v>8</v>
       </c>
       <c r="X43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y43">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -4153,7 +4153,7 @@
         <v>8</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L44">
         <v>7</v>
@@ -4162,37 +4162,37 @@
         <v>6</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T44">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U44">
         <v>7</v>
       </c>
       <c r="V44">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W44">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y44">
         <v>6</v>
@@ -4239,37 +4239,37 @@
         <v>6</v>
       </c>
       <c r="N45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W45">
         <v>8</v>
       </c>
       <c r="X45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y45">
         <v>6</v>
@@ -4313,43 +4313,43 @@
         <v>6</v>
       </c>
       <c r="M46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T46">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V46">
         <v>6</v>
       </c>
       <c r="W46">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y46">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4405,7 +4405,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
@@ -4414,19 +4414,19 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>72.09</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="G2">
-        <v>27.91</v>
+        <v>23.26</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4437,7 +4437,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -4446,30 +4446,30 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>72.09</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G3">
-        <v>25.58</v>
+        <v>18.6</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>2.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -4478,16 +4478,16 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>79.06999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G4">
-        <v>20.93</v>
+        <v>18.6</v>
       </c>
       <c r="H4">
         <v>7.4</v>
@@ -4501,7 +4501,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
@@ -4510,30 +4510,30 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>83.72</v>
+        <v>86.05</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>13.95</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>16.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
@@ -4545,22 +4545,22 @@
         <v>38</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F6">
         <v>88.37</v>
       </c>
       <c r="G6">
-        <v>2.33</v>
+        <v>11.63</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4574,19 +4574,19 @@
         <v>43</v>
       </c>
       <c r="D7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>90.7</v>
+        <v>93.02</v>
       </c>
       <c r="G7">
-        <v>9.300000000000001</v>
+        <v>6.98</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4602,7 +4602,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4627,246 +4627,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920252</v>
-      </c>
-      <c r="B2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920261</v>
-      </c>
-      <c r="B3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920261</v>
-      </c>
-      <c r="B4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920265</v>
-      </c>
-      <c r="B5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920265</v>
-      </c>
-      <c r="B6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920269</v>
-      </c>
-      <c r="B7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920269</v>
-      </c>
-      <c r="B8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920273</v>
-      </c>
-      <c r="B9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920274</v>
-      </c>
-      <c r="B10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920281</v>
-      </c>
-      <c r="B11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" t="s">
-        <v>94</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920282</v>
-      </c>
-      <c r="B12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920285</v>
-      </c>
-      <c r="B13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" t="s">
-        <v>96</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -4902,166 +4662,166 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920261</v>
+        <v>21330051920251</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>139</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920265</v>
+        <v>21330051920252</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920269</v>
+        <v>21330051920253</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>141</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920252</v>
+        <v>21330051920254</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920273</v>
+        <v>21330051920255</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920274</v>
+        <v>21330051920256</v>
       </c>
       <c r="B7" t="s">
         <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920281</v>
+        <v>21330051920257</v>
       </c>
       <c r="B8" t="s">
         <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>145</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920282</v>
+        <v>21330051920258</v>
       </c>
       <c r="B9" t="s">
         <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920285</v>
+        <v>21330051920259</v>
       </c>
       <c r="B10" t="s">
         <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920251</v>
+        <v>21330051920260</v>
       </c>
       <c r="B11" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D11" t="s">
         <v>148</v>
@@ -5072,13 +4832,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920253</v>
+        <v>21330051920261</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
         <v>149</v>
@@ -5089,13 +4849,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920254</v>
+        <v>21330051920360</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D13" t="s">
         <v>150</v>
@@ -5106,13 +4866,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920255</v>
+        <v>21330051920262</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s">
         <v>151</v>
@@ -5123,16 +4883,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920256</v>
+        <v>21330051920263</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D15" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -5140,16 +4900,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920257</v>
+        <v>21330051920264</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D16" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -5157,16 +4917,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920258</v>
+        <v>21330051920265</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -5174,16 +4934,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920259</v>
+        <v>21330051920266</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
         <v>83</v>
       </c>
       <c r="D18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -5191,16 +4951,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920260</v>
+        <v>21330051920267</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -5208,16 +4968,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920360</v>
+        <v>21330051920358</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5225,16 +4985,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920262</v>
+        <v>21330051920268</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -5242,16 +5002,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920263</v>
+        <v>21330051920269</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="D22" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -5259,13 +5019,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920264</v>
+        <v>21330051920270</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
         <v>159</v>
@@ -5276,13 +5036,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920266</v>
+        <v>21330051920271</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="D24" t="s">
         <v>160</v>
@@ -5293,13 +5053,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920267</v>
+        <v>21330051920272</v>
       </c>
       <c r="B25" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D25" t="s">
         <v>161</v>
@@ -5310,13 +5070,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920358</v>
+        <v>21330051920273</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D26" t="s">
         <v>162</v>
@@ -5327,13 +5087,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920268</v>
+        <v>21330051920274</v>
       </c>
       <c r="B27" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="D27" t="s">
         <v>163</v>
@@ -5344,13 +5104,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920270</v>
+        <v>21330051920361</v>
       </c>
       <c r="B28" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s">
         <v>164</v>
@@ -5361,13 +5121,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920271</v>
+        <v>21330051920275</v>
       </c>
       <c r="B29" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s">
         <v>165</v>
@@ -5378,13 +5138,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920272</v>
+        <v>21330051920362</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s">
         <v>166</v>
@@ -5395,13 +5155,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920361</v>
+        <v>21330051920276</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="D31" t="s">
         <v>167</v>
@@ -5412,13 +5172,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920275</v>
+        <v>21330051920277</v>
       </c>
       <c r="B32" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>83</v>
+        <v>132</v>
       </c>
       <c r="D32" t="s">
         <v>168</v>
@@ -5429,13 +5189,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920362</v>
+        <v>21330051920278</v>
       </c>
       <c r="B33" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="C33" t="s">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
         <v>169</v>
@@ -5446,13 +5206,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920276</v>
+        <v>21330051920279</v>
       </c>
       <c r="B34" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="C34" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D34" t="s">
         <v>170</v>
@@ -5463,13 +5223,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920277</v>
+        <v>21330051920280</v>
       </c>
       <c r="B35" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
         <v>171</v>
@@ -5480,13 +5240,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920278</v>
+        <v>21330051920281</v>
       </c>
       <c r="B36" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="D36" t="s">
         <v>172</v>
@@ -5497,13 +5257,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920279</v>
+        <v>21330051920282</v>
       </c>
       <c r="B37" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C37" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="D37" t="s">
         <v>173</v>
@@ -5514,13 +5274,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920280</v>
+        <v>21330051920283</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="D38" t="s">
         <v>174</v>
@@ -5531,13 +5291,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920283</v>
+        <v>21330051920284</v>
       </c>
       <c r="B39" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C39" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="D39" t="s">
         <v>175</v>
@@ -5548,13 +5308,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>21330051920284</v>
+        <v>21330051920285</v>
       </c>
       <c r="B40" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="C40" t="s">
-        <v>144</v>
+        <v>95</v>
       </c>
       <c r="D40" t="s">
         <v>176</v>
@@ -5568,10 +5328,10 @@
         <v>21330051920286</v>
       </c>
       <c r="B41" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D41" t="s">
         <v>177</v>
@@ -5585,10 +5345,10 @@
         <v>20330051920358</v>
       </c>
       <c r="B42" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C42" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D42" t="s">
         <v>178</v>
@@ -5602,10 +5362,10 @@
         <v>21330051920287</v>
       </c>
       <c r="B43" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C43" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D43" t="s">
         <v>179</v>
@@ -5619,10 +5379,10 @@
         <v>21330051920288</v>
       </c>
       <c r="B44" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C44" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D44" t="s">
         <v>180</v>
@@ -5638,7 +5398,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5670,162 +5430,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920284</v>
+        <v>21330051920287</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>64</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920284</v>
-      </c>
-      <c r="B3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920288</v>
-      </c>
-      <c r="B4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C4" t="s">
-        <v>147</v>
-      </c>
-      <c r="D4" t="s">
-        <v>180</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920288</v>
-      </c>
-      <c r="B5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D5" t="s">
-        <v>180</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>64</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920253</v>
-      </c>
-      <c r="B6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" t="s">
-        <v>125</v>
-      </c>
-      <c r="D6" t="s">
-        <v>149</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920271</v>
-      </c>
-      <c r="B7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" t="s">
-        <v>138</v>
-      </c>
-      <c r="D7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920277</v>
-      </c>
-      <c r="B8" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" t="s">
-        <v>142</v>
-      </c>
-      <c r="D8" t="s">
-        <v>171</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G8">
         <v>5</v>
       </c>
     </row>
